--- a/WiFi_Monitor_Database.xlsx
+++ b/WiFi_Monitor_Database.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="8" min="1" max="1"/>
@@ -976,13 +976,113 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="9">
-      <c r="B6" s="16" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Signal (RSSI)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:00:27</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>v2 revision (adds SNR term, weights renormalized) - see ScoringEngine.kt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Latency</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:00:27</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>v2 revision (adds SNR term, weights renormalized) - see ScoringEngine.kt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Packet Loss</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:00:27</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>v2 revision (adds SNR term, weights renormalized) - see ScoringEngine.kt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:00:27</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>v2 revision (adds SNR term, weights renormalized) - see ScoringEngine.kt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SNR (link-speed proxy)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:00:27</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>v2 revision (adds SNR term, weights renormalized) - see ScoringEngine.kt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Sum:</t>
         </is>
       </c>
-      <c r="C6" s="17">
-        <f>SUM(B2:B5)</f>
+      <c r="C11" s="17">
+        <f>SUM(B6:B10)</f>
         <v/>
       </c>
     </row>
